--- a/dados/territorio.xlsx
+++ b/dados/territorio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pmemaquinascnh.sharepoint.com/sites/Marketing-PME/Shared Documents/Inteligência Comercial/Projeto Horizonte/MatrizPerformanceDashboard/dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_B0C3667B85C978711F8723A16F259F858525228C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{068BF177-65CB-4B47-9A1B-D6FD0CD4A836}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C318D21-B0BF-438A-9C25-7B7DEC01B44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6516" uniqueCount="983">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6516" uniqueCount="985">
   <si>
     <t>Código IBGE</t>
   </si>
@@ -2985,6 +2985,12 @@
   </si>
   <si>
     <t>WESLEY.LIMA</t>
+  </si>
+  <si>
+    <t>NATALIA FATIMA MORAES</t>
+  </si>
+  <si>
+    <t>NATALIA.MORAES</t>
   </si>
 </sst>
 </file>
@@ -3085,7 +3091,79 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF70AD47"/>
+          <bgColor rgb="FF70AD47"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3433,54 +3511,6 @@
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE2EFDA"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF70AD47"/>
-          <bgColor rgb="FF70AD47"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3495,25 +3525,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F1FEB497-9701-4180-9E5F-E582B822EF71}" name="Table1" displayName="Table1" ref="A1:N592" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F1FEB497-9701-4180-9E5F-E582B822EF71}" name="Table1" displayName="Table1" ref="A1:O592" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+  <autoFilter ref="A1:O592" xr:uid="{F1FEB497-9701-4180-9E5F-E582B822EF71}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N592">
     <sortCondition ref="H1:H592"/>
   </sortState>
-  <tableColumns count="14">
-    <tableColumn id="2" xr3:uid="{336287FE-5AE8-4712-BC59-3BF196550C99}" name="Código IBGE" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{332A869B-817E-415E-8024-7AB2AD30BC5C}" name="Município IBGE" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{866808A4-0228-4685-98DF-AF794AC14A96}" name="Município SEM ACENTO" dataDxfId="11"/>
-    <tableColumn id="1" xr3:uid="{FBADD9F0-B652-48D4-83CC-15EDC6C69E72}" name="UF" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{277848D9-FCAC-49AB-9C71-11D3A1C71ABB}" name="Filial" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{838D7233-93F8-4CE4-8681-8FC977C930A8}" name="Região" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{BBB8672E-A46E-4A38-BA06-4719D84B598B}" name="Marca" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{8A6250E1-55C7-4B4D-9897-D63C75F780CE}" name="Vendedor" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{52A0B939-3437-4A61-96B4-04EE87855F2B}" name="NOME CRM" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{C2D28213-D9EE-4BF0-8D43-48EE81A2BF66}" name="NOME BI" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{1D8D9ADF-0F5F-4EF3-BF66-66BE799636C2}" name="DIVIDE?" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{565ECC43-B9E9-4BD1-A879-C7CC21B0C0F0}" name="QTS PARTES?" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{CC051FAC-1850-4794-BC19-35B8E56E1CC4}" name="Código MUN PME" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{B2961501-921E-4B58-B590-3507C31B810C}" name="% MUN" dataDxfId="0"/>
+  <tableColumns count="15">
+    <tableColumn id="2" xr3:uid="{336287FE-5AE8-4712-BC59-3BF196550C99}" name="Código IBGE" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{332A869B-817E-415E-8024-7AB2AD30BC5C}" name="Município IBGE" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{866808A4-0228-4685-98DF-AF794AC14A96}" name="Município SEM ACENTO" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{FBADD9F0-B652-48D4-83CC-15EDC6C69E72}" name="UF" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{277848D9-FCAC-49AB-9C71-11D3A1C71ABB}" name="Filial" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{838D7233-93F8-4CE4-8681-8FC977C930A8}" name="Região" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{BBB8672E-A46E-4A38-BA06-4719D84B598B}" name="Marca" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{8A6250E1-55C7-4B4D-9897-D63C75F780CE}" name="Vendedor" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{52A0B939-3437-4A61-96B4-04EE87855F2B}" name="NOME CRM" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{C2D28213-D9EE-4BF0-8D43-48EE81A2BF66}" name="NOME BI" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{1D8D9ADF-0F5F-4EF3-BF66-66BE799636C2}" name="DIVIDE?" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{565ECC43-B9E9-4BD1-A879-C7CC21B0C0F0}" name="QTS PARTES?" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{CC051FAC-1850-4794-BC19-35B8E56E1CC4}" name="Código MUN PME" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{B2961501-921E-4B58-B590-3507C31B810C}" name="% MUN" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{D3455544-E52E-49C1-8737-47AE54DBFC05}" name="CÓD_ÁREA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9101,13 +9133,13 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
-        <v>3111705</v>
+        <v>3100401</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>16</v>
@@ -9137,7 +9169,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="5">
-        <v>3111705</v>
+        <v>3100401</v>
       </c>
       <c r="N114" s="7">
         <v>1</v>
@@ -9148,13 +9180,13 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>3148806</v>
+        <v>3102308</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>16</v>
@@ -9184,7 +9216,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="5">
-        <v>3148806</v>
+        <v>3102308</v>
       </c>
       <c r="N115" s="7">
         <v>1</v>
@@ -9195,13 +9227,13 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>3100401</v>
+        <v>3103702</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>16</v>
@@ -9231,7 +9263,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="5">
-        <v>3100401</v>
+        <v>3103702</v>
       </c>
       <c r="N116" s="7">
         <v>1</v>
@@ -9242,13 +9274,13 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
-        <v>3102308</v>
+        <v>3105707</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>16</v>
@@ -9278,7 +9310,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="5">
-        <v>3102308</v>
+        <v>3105707</v>
       </c>
       <c r="N117" s="7">
         <v>1</v>
@@ -9289,13 +9321,13 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
-        <v>3103702</v>
+        <v>3115359</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>16</v>
@@ -9325,7 +9357,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="5">
-        <v>3103702</v>
+        <v>3115359</v>
       </c>
       <c r="N118" s="7">
         <v>1</v>
@@ -9336,13 +9368,13 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
-        <v>3105707</v>
+        <v>3122702</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>16</v>
@@ -9372,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="5">
-        <v>3105707</v>
+        <v>3122702</v>
       </c>
       <c r="N119" s="7">
         <v>1</v>
@@ -9383,13 +9415,13 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
-        <v>3115359</v>
+        <v>3135506</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>16</v>
@@ -9419,7 +9451,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="5">
-        <v>3115359</v>
+        <v>3135506</v>
       </c>
       <c r="N120" s="7">
         <v>1</v>
@@ -9430,13 +9462,13 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
-        <v>3122702</v>
+        <v>3145851</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>16</v>
@@ -9466,7 +9498,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="5">
-        <v>3122702</v>
+        <v>3145851</v>
       </c>
       <c r="N121" s="7">
         <v>1</v>
@@ -9477,13 +9509,13 @@
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
-        <v>3135506</v>
+        <v>3150208</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>16</v>
@@ -9513,7 +9545,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="5">
-        <v>3135506</v>
+        <v>3150208</v>
       </c>
       <c r="N122" s="7">
         <v>1</v>
@@ -9524,13 +9556,13 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
-        <v>3145851</v>
+        <v>3152105</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>16</v>
@@ -9560,7 +9592,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="5">
-        <v>3145851</v>
+        <v>3152105</v>
       </c>
       <c r="N123" s="7">
         <v>1</v>
@@ -9571,13 +9603,13 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
-        <v>3150208</v>
+        <v>3154903</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>16</v>
@@ -9607,7 +9639,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="5">
-        <v>3150208</v>
+        <v>3154903</v>
       </c>
       <c r="N124" s="7">
         <v>1</v>
@@ -9618,13 +9650,13 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
-        <v>3152105</v>
+        <v>3155009</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>16</v>
@@ -9654,7 +9686,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="5">
-        <v>3152105</v>
+        <v>3155009</v>
       </c>
       <c r="N125" s="7">
         <v>1</v>
@@ -9665,13 +9697,13 @@
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
-        <v>3154903</v>
+        <v>3155702</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>16</v>
@@ -9701,7 +9733,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="5">
-        <v>3154903</v>
+        <v>3155702</v>
       </c>
       <c r="N126" s="7">
         <v>1</v>
@@ -9712,13 +9744,13 @@
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
-        <v>3155009</v>
+        <v>3157401</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>16</v>
@@ -9748,7 +9780,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="5">
-        <v>3155009</v>
+        <v>3157401</v>
       </c>
       <c r="N127" s="7">
         <v>1</v>
@@ -9759,13 +9791,13 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
-        <v>3155702</v>
+        <v>3160108</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>16</v>
@@ -9795,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="5">
-        <v>3155702</v>
+        <v>3160108</v>
       </c>
       <c r="N128" s="7">
         <v>1</v>
@@ -9806,13 +9838,13 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
-        <v>3157401</v>
+        <v>3161007</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>16</v>
@@ -9842,7 +9874,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="5">
-        <v>3157401</v>
+        <v>3161007</v>
       </c>
       <c r="N129" s="7">
         <v>1</v>
@@ -9853,13 +9885,13 @@
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
-        <v>3160108</v>
+        <v>3164001</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>16</v>
@@ -9889,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="5">
-        <v>3160108</v>
+        <v>3164001</v>
       </c>
       <c r="N130" s="7">
         <v>1</v>
@@ -9900,13 +9932,13 @@
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
-        <v>3161007</v>
+        <v>3165560</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>16</v>
@@ -9936,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="5">
-        <v>3161007</v>
+        <v>3165560</v>
       </c>
       <c r="N131" s="7">
         <v>1</v>
@@ -9947,13 +9979,13 @@
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
-        <v>3164001</v>
+        <v>3170503</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>16</v>
@@ -9983,7 +10015,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="5">
-        <v>3164001</v>
+        <v>3170503</v>
       </c>
       <c r="N132" s="7">
         <v>1</v>
@@ -9994,13 +10026,13 @@
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
-        <v>3165560</v>
+        <v>3103108</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>227</v>
+        <v>462</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>227</v>
+        <v>463</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>16</v>
@@ -10015,13 +10047,13 @@
         <v>19</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="I133" s="5" t="s">
-        <v>199</v>
+        <v>464</v>
+      </c>
+      <c r="I133" s="8" t="s">
+        <v>465</v>
       </c>
       <c r="J133" s="5" t="s">
-        <v>957</v>
+        <v>968</v>
       </c>
       <c r="K133" s="5" t="s">
         <v>21</v>
@@ -10030,24 +10062,24 @@
         <v>0</v>
       </c>
       <c r="M133" s="5">
-        <v>3165560</v>
+        <v>3103108</v>
       </c>
       <c r="N133" s="7">
         <v>1</v>
       </c>
       <c r="O133" s="6" t="s">
-        <v>200</v>
+        <v>466</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
-        <v>3170503</v>
+        <v>3110103</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>228</v>
+        <v>467</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>229</v>
+        <v>467</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>16</v>
@@ -10062,13 +10094,13 @@
         <v>19</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="I134" s="5" t="s">
-        <v>199</v>
+        <v>464</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>465</v>
       </c>
       <c r="J134" s="5" t="s">
-        <v>957</v>
+        <v>968</v>
       </c>
       <c r="K134" s="5" t="s">
         <v>21</v>
@@ -10077,13 +10109,13 @@
         <v>0</v>
       </c>
       <c r="M134" s="5">
-        <v>3170503</v>
+        <v>3110103</v>
       </c>
       <c r="N134" s="7">
         <v>1</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>200</v>
+        <v>466</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
@@ -16198,19 +16230,19 @@
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
-        <v>2200806</v>
+        <v>2903201</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>440</v>
+        <v>242</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>441</v>
+        <v>242</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>305</v>
+        <v>87</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="F265" s="6" t="s">
         <v>129</v>
@@ -16219,39 +16251,39 @@
         <v>19</v>
       </c>
       <c r="H265" s="5" t="s">
-        <v>708</v>
+        <v>442</v>
       </c>
       <c r="I265" s="5" t="s">
-        <v>708</v>
+        <v>442</v>
       </c>
       <c r="J265" s="5" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="K265" s="5" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L265" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M265" s="5">
-        <v>2200806</v>
+        <v>29032013</v>
       </c>
       <c r="N265" s="7">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="O265" s="6" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
-        <v>2903201</v>
+        <v>2926202</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>242</v>
+        <v>444</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>242</v>
+        <v>445</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>87</v>
@@ -16278,13 +16310,13 @@
         <v>83</v>
       </c>
       <c r="L266" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M266" s="5">
-        <v>29032013</v>
+        <v>29262022</v>
       </c>
       <c r="N266" s="7">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="O266" s="6" t="s">
         <v>443</v>
@@ -16292,60 +16324,60 @@
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
-        <v>2926202</v>
+        <v>2912806</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>87</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="F267" s="6" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="G267" s="6" t="s">
         <v>19</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="I267" s="5" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="J267" s="5" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="K267" s="5" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L267" s="5">
         <v>0</v>
       </c>
       <c r="M267" s="5">
-        <v>29262022</v>
+        <v>2912806</v>
       </c>
       <c r="N267" s="7">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O267" s="6" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="268" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
-        <v>2912806</v>
+        <v>2916005</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>87</v>
@@ -16375,7 +16407,7 @@
         <v>0</v>
       </c>
       <c r="M268" s="5">
-        <v>2912806</v>
+        <v>2916005</v>
       </c>
       <c r="N268" s="7">
         <v>1</v>
@@ -16386,13 +16418,13 @@
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
-        <v>2916005</v>
+        <v>2918902</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>87</v>
@@ -16422,7 +16454,7 @@
         <v>0</v>
       </c>
       <c r="M269" s="5">
-        <v>2916005</v>
+        <v>2918902</v>
       </c>
       <c r="N269" s="7">
         <v>1</v>
@@ -16433,13 +16465,13 @@
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
-        <v>2918902</v>
+        <v>2921104</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D270" s="4" t="s">
         <v>87</v>
@@ -16469,7 +16501,7 @@
         <v>0</v>
       </c>
       <c r="M270" s="5">
-        <v>2918902</v>
+        <v>2921104</v>
       </c>
       <c r="N270" s="7">
         <v>1</v>
@@ -16480,13 +16512,13 @@
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
-        <v>2921104</v>
+        <v>2922003</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>87</v>
@@ -16516,7 +16548,7 @@
         <v>0</v>
       </c>
       <c r="M271" s="5">
-        <v>2921104</v>
+        <v>2922003</v>
       </c>
       <c r="N271" s="7">
         <v>1</v>
@@ -16527,13 +16559,13 @@
     </row>
     <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
-        <v>2922003</v>
+        <v>2923001</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>87</v>
@@ -16563,7 +16595,7 @@
         <v>0</v>
       </c>
       <c r="M272" s="5">
-        <v>2922003</v>
+        <v>2923001</v>
       </c>
       <c r="N272" s="7">
         <v>1</v>
@@ -16574,13 +16606,13 @@
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
-        <v>2923001</v>
+        <v>2933257</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>87</v>
@@ -16610,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="M273" s="5">
-        <v>2923001</v>
+        <v>2933257</v>
       </c>
       <c r="N273" s="7">
         <v>1</v>
@@ -16621,19 +16653,19 @@
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" s="4">
-        <v>2933257</v>
+        <v>3112109</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F274" s="6" t="s">
         <v>18</v>
@@ -16642,13 +16674,13 @@
         <v>19</v>
       </c>
       <c r="H274" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="I274" s="5" t="s">
-        <v>448</v>
+        <v>464</v>
+      </c>
+      <c r="I274" s="8" t="s">
+        <v>465</v>
       </c>
       <c r="J274" s="5" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="K274" s="5" t="s">
         <v>21</v>
@@ -16657,24 +16689,24 @@
         <v>0</v>
       </c>
       <c r="M274" s="5">
-        <v>2933257</v>
+        <v>3112109</v>
       </c>
       <c r="N274" s="7">
         <v>1</v>
       </c>
       <c r="O274" s="6" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
-        <v>3103108</v>
+        <v>3113305</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>16</v>
@@ -16704,7 +16736,7 @@
         <v>0</v>
       </c>
       <c r="M275" s="5">
-        <v>3103108</v>
+        <v>3113305</v>
       </c>
       <c r="N275" s="7">
         <v>1</v>
@@ -16715,13 +16747,13 @@
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" s="4">
-        <v>3110103</v>
+        <v>3122009</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>16</v>
@@ -16751,7 +16783,7 @@
         <v>0</v>
       </c>
       <c r="M276" s="5">
-        <v>3110103</v>
+        <v>3122009</v>
       </c>
       <c r="N276" s="7">
         <v>1</v>
@@ -16762,13 +16794,13 @@
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
-        <v>3112109</v>
+        <v>3124203</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>16</v>
@@ -16798,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="M277" s="5">
-        <v>3112109</v>
+        <v>3124203</v>
       </c>
       <c r="N277" s="7">
         <v>1</v>
@@ -16809,13 +16841,13 @@
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
-        <v>3113305</v>
+        <v>3124906</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>16</v>
@@ -16845,7 +16877,7 @@
         <v>0</v>
       </c>
       <c r="M278" s="5">
-        <v>3113305</v>
+        <v>3124906</v>
       </c>
       <c r="N278" s="7">
         <v>1</v>
@@ -16856,13 +16888,13 @@
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
-        <v>3122009</v>
+        <v>3125309</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>16</v>
@@ -16892,7 +16924,7 @@
         <v>0</v>
       </c>
       <c r="M279" s="5">
-        <v>3122009</v>
+        <v>3125309</v>
       </c>
       <c r="N279" s="7">
         <v>1</v>
@@ -16903,13 +16935,13 @@
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
-        <v>3124203</v>
+        <v>3125952</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D280" s="4" t="s">
         <v>16</v>
@@ -16939,7 +16971,7 @@
         <v>0</v>
       </c>
       <c r="M280" s="5">
-        <v>3124203</v>
+        <v>3125952</v>
       </c>
       <c r="N280" s="7">
         <v>1</v>
@@ -16950,13 +16982,13 @@
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
-        <v>3124906</v>
+        <v>3142106</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>16</v>
@@ -16986,7 +17018,7 @@
         <v>0</v>
       </c>
       <c r="M281" s="5">
-        <v>3124906</v>
+        <v>3142106</v>
       </c>
       <c r="N281" s="7">
         <v>1</v>
@@ -16997,13 +17029,13 @@
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
-        <v>3125309</v>
+        <v>3145877</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>16</v>
@@ -17033,7 +17065,7 @@
         <v>0</v>
       </c>
       <c r="M282" s="5">
-        <v>3125309</v>
+        <v>3145877</v>
       </c>
       <c r="N282" s="7">
         <v>1</v>
@@ -17044,13 +17076,13 @@
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
-        <v>3125952</v>
+        <v>3149002</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D283" s="4" t="s">
         <v>16</v>
@@ -17080,7 +17112,7 @@
         <v>0</v>
       </c>
       <c r="M283" s="5">
-        <v>3125952</v>
+        <v>3149002</v>
       </c>
       <c r="N283" s="7">
         <v>1</v>
@@ -17091,13 +17123,13 @@
     </row>
     <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
-        <v>3142106</v>
+        <v>3161403</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D284" s="4" t="s">
         <v>16</v>
@@ -17127,7 +17159,7 @@
         <v>0</v>
       </c>
       <c r="M284" s="5">
-        <v>3142106</v>
+        <v>3161403</v>
       </c>
       <c r="N284" s="7">
         <v>1</v>
@@ -17138,13 +17170,13 @@
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
-        <v>3145877</v>
+        <v>3169208</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>16</v>
@@ -17174,7 +17206,7 @@
         <v>0</v>
       </c>
       <c r="M285" s="5">
-        <v>3145877</v>
+        <v>3169208</v>
       </c>
       <c r="N285" s="7">
         <v>1</v>
@@ -17185,13 +17217,13 @@
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
-        <v>3148202</v>
+        <v>3171402</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>16</v>
@@ -17221,7 +17253,7 @@
         <v>0</v>
       </c>
       <c r="M286" s="5">
-        <v>3148202</v>
+        <v>3171402</v>
       </c>
       <c r="N286" s="7">
         <v>1</v>
@@ -17232,13 +17264,13 @@
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
-        <v>3149002</v>
+        <v>3111705</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>482</v>
+        <v>201</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>482</v>
+        <v>202</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>16</v>
@@ -17253,13 +17285,13 @@
         <v>19</v>
       </c>
       <c r="H287" s="5" t="s">
-        <v>464</v>
+        <v>532</v>
       </c>
       <c r="I287" s="8" t="s">
-        <v>465</v>
+        <v>533</v>
       </c>
       <c r="J287" s="5" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="K287" s="5" t="s">
         <v>21</v>
@@ -17268,24 +17300,24 @@
         <v>0</v>
       </c>
       <c r="M287" s="5">
-        <v>3149002</v>
+        <v>3111705</v>
       </c>
       <c r="N287" s="7">
         <v>1</v>
       </c>
       <c r="O287" s="6" t="s">
-        <v>466</v>
+        <v>200</v>
       </c>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
-        <v>3161403</v>
+        <v>3148806</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>483</v>
+        <v>203</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>484</v>
+        <v>203</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>16</v>
@@ -17300,13 +17332,13 @@
         <v>19</v>
       </c>
       <c r="H288" s="5" t="s">
-        <v>464</v>
+        <v>532</v>
       </c>
       <c r="I288" s="8" t="s">
-        <v>465</v>
+        <v>533</v>
       </c>
       <c r="J288" s="5" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="K288" s="5" t="s">
         <v>21</v>
@@ -17315,24 +17347,24 @@
         <v>0</v>
       </c>
       <c r="M288" s="5">
-        <v>3161403</v>
+        <v>3148806</v>
       </c>
       <c r="N288" s="7">
         <v>1</v>
       </c>
       <c r="O288" s="6" t="s">
-        <v>466</v>
+        <v>200</v>
       </c>
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
-        <v>3169208</v>
+        <v>3148202</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D289" s="4" t="s">
         <v>16</v>
@@ -17347,13 +17379,13 @@
         <v>19</v>
       </c>
       <c r="H289" s="5" t="s">
-        <v>464</v>
+        <v>532</v>
       </c>
       <c r="I289" s="8" t="s">
-        <v>465</v>
+        <v>533</v>
       </c>
       <c r="J289" s="5" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="K289" s="5" t="s">
         <v>21</v>
@@ -17362,7 +17394,7 @@
         <v>0</v>
       </c>
       <c r="M289" s="5">
-        <v>3169208</v>
+        <v>3148202</v>
       </c>
       <c r="N289" s="7">
         <v>1</v>
@@ -17373,19 +17405,19 @@
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
-        <v>3171402</v>
+        <v>2906907</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="E290" s="5" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F290" s="6" t="s">
         <v>18</v>
@@ -17394,13 +17426,13 @@
         <v>19</v>
       </c>
       <c r="H290" s="5" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="I290" s="8" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="J290" s="5" t="s">
-        <v>968</v>
+        <v>490</v>
       </c>
       <c r="K290" s="5" t="s">
         <v>21</v>
@@ -17409,24 +17441,24 @@
         <v>0</v>
       </c>
       <c r="M290" s="5">
-        <v>3171402</v>
+        <v>2906907</v>
       </c>
       <c r="N290" s="7">
         <v>1</v>
       </c>
       <c r="O290" s="6" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
-        <v>2906907</v>
+        <v>2931350</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>87</v>
@@ -17456,7 +17488,7 @@
         <v>0</v>
       </c>
       <c r="M291" s="5">
-        <v>2906907</v>
+        <v>2931350</v>
       </c>
       <c r="N291" s="7">
         <v>1</v>
@@ -17467,19 +17499,19 @@
     </row>
     <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
-        <v>2931350</v>
+        <v>3201308</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E292" s="5" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="F292" s="6" t="s">
         <v>18</v>
@@ -17488,7 +17520,7 @@
         <v>19</v>
       </c>
       <c r="H292" s="5" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="I292" s="8" t="s">
         <v>490</v>
@@ -17503,24 +17535,24 @@
         <v>0</v>
       </c>
       <c r="M292" s="5">
-        <v>2931350</v>
+        <v>3201308</v>
       </c>
       <c r="N292" s="7">
         <v>1</v>
       </c>
       <c r="O292" s="6" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
-        <v>3201308</v>
+        <v>3202405</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>78</v>
@@ -17550,7 +17582,7 @@
         <v>0</v>
       </c>
       <c r="M293" s="5">
-        <v>3201308</v>
+        <v>3202405</v>
       </c>
       <c r="N293" s="7">
         <v>1</v>
@@ -17561,13 +17593,13 @@
     </row>
     <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
-        <v>3202405</v>
+        <v>3205101</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>78</v>
@@ -17597,7 +17629,7 @@
         <v>0</v>
       </c>
       <c r="M294" s="5">
-        <v>3202405</v>
+        <v>3205101</v>
       </c>
       <c r="N294" s="7">
         <v>1</v>
@@ -17608,13 +17640,13 @@
     </row>
     <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
-        <v>3205101</v>
+        <v>3205200</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>78</v>
@@ -17644,7 +17676,7 @@
         <v>0</v>
       </c>
       <c r="M295" s="5">
-        <v>3205101</v>
+        <v>3205200</v>
       </c>
       <c r="N295" s="7">
         <v>1</v>
@@ -17655,13 +17687,13 @@
     </row>
     <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
-        <v>3205200</v>
+        <v>3205309</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>78</v>
@@ -17691,7 +17723,7 @@
         <v>0</v>
       </c>
       <c r="M296" s="5">
-        <v>3205200</v>
+        <v>3205309</v>
       </c>
       <c r="N296" s="7">
         <v>1</v>
@@ -17702,19 +17734,19 @@
     </row>
     <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
-        <v>3205309</v>
+        <v>3300209</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="E297" s="5" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="F297" s="6" t="s">
         <v>18</v>
@@ -17723,13 +17755,13 @@
         <v>19</v>
       </c>
       <c r="H297" s="5" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="I297" s="8" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="J297" s="5" t="s">
-        <v>490</v>
+        <v>969</v>
       </c>
       <c r="K297" s="5" t="s">
         <v>21</v>
@@ -17738,24 +17770,24 @@
         <v>0</v>
       </c>
       <c r="M297" s="5">
-        <v>3205309</v>
+        <v>3300209</v>
       </c>
       <c r="N297" s="7">
         <v>1</v>
       </c>
       <c r="O297" s="6" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
-        <v>3300209</v>
+        <v>3300506</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>252</v>
@@ -17785,7 +17817,7 @@
         <v>0</v>
       </c>
       <c r="M298" s="5">
-        <v>3300209</v>
+        <v>3300506</v>
       </c>
       <c r="N298" s="7">
         <v>1</v>
@@ -17796,13 +17828,13 @@
     </row>
     <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
-        <v>3300506</v>
+        <v>3300803</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>252</v>
@@ -17832,7 +17864,7 @@
         <v>0</v>
       </c>
       <c r="M299" s="5">
-        <v>3300506</v>
+        <v>3300803</v>
       </c>
       <c r="N299" s="7">
         <v>1</v>
@@ -17843,13 +17875,13 @@
     </row>
     <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
-        <v>3300803</v>
+        <v>3301207</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>252</v>
@@ -17879,7 +17911,7 @@
         <v>0</v>
       </c>
       <c r="M300" s="5">
-        <v>3300803</v>
+        <v>3301207</v>
       </c>
       <c r="N300" s="7">
         <v>1</v>
@@ -17890,13 +17922,13 @@
     </row>
     <row r="301" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
-        <v>3301207</v>
+        <v>3301603</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>252</v>
@@ -17926,7 +17958,7 @@
         <v>0</v>
       </c>
       <c r="M301" s="5">
-        <v>3301207</v>
+        <v>3301603</v>
       </c>
       <c r="N301" s="7">
         <v>1</v>
@@ -17937,13 +17969,13 @@
     </row>
     <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
-        <v>3301603</v>
+        <v>3301850</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>252</v>
@@ -17973,7 +18005,7 @@
         <v>0</v>
       </c>
       <c r="M302" s="5">
-        <v>3301603</v>
+        <v>3301850</v>
       </c>
       <c r="N302" s="7">
         <v>1</v>
@@ -17984,13 +18016,13 @@
     </row>
     <row r="303" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
-        <v>3301850</v>
+        <v>3301900</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>252</v>
@@ -18020,7 +18052,7 @@
         <v>0</v>
       </c>
       <c r="M303" s="5">
-        <v>3301850</v>
+        <v>3301900</v>
       </c>
       <c r="N303" s="7">
         <v>1</v>
@@ -18031,13 +18063,13 @@
     </row>
     <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
-        <v>3301900</v>
+        <v>3302502</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>252</v>
@@ -18067,7 +18099,7 @@
         <v>0</v>
       </c>
       <c r="M304" s="5">
-        <v>3301900</v>
+        <v>3302502</v>
       </c>
       <c r="N304" s="7">
         <v>1</v>
@@ -18078,13 +18110,13 @@
     </row>
     <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
-        <v>3302502</v>
+        <v>3302700</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>252</v>
@@ -18114,7 +18146,7 @@
         <v>0</v>
       </c>
       <c r="M305" s="5">
-        <v>3302502</v>
+        <v>3302700</v>
       </c>
       <c r="N305" s="7">
         <v>1</v>
@@ -18125,13 +18157,13 @@
     </row>
     <row r="306" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
-        <v>3302700</v>
+        <v>3303302</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>252</v>
@@ -18161,7 +18193,7 @@
         <v>0</v>
       </c>
       <c r="M306" s="5">
-        <v>3302700</v>
+        <v>3303302</v>
       </c>
       <c r="N306" s="7">
         <v>1</v>
@@ -18172,13 +18204,13 @@
     </row>
     <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
-        <v>3303302</v>
+        <v>3303401</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>252</v>
@@ -18208,7 +18240,7 @@
         <v>0</v>
       </c>
       <c r="M307" s="5">
-        <v>3303302</v>
+        <v>3303401</v>
       </c>
       <c r="N307" s="7">
         <v>1</v>
@@ -18219,13 +18251,13 @@
     </row>
     <row r="308" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A308" s="4">
-        <v>3303401</v>
+        <v>3304300</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>252</v>
@@ -18255,7 +18287,7 @@
         <v>0</v>
       </c>
       <c r="M308" s="5">
-        <v>3303401</v>
+        <v>3304300</v>
       </c>
       <c r="N308" s="7">
         <v>1</v>
@@ -18266,13 +18298,13 @@
     </row>
     <row r="309" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
-        <v>3304300</v>
+        <v>3304904</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>252</v>
@@ -18302,7 +18334,7 @@
         <v>0</v>
       </c>
       <c r="M309" s="5">
-        <v>3304300</v>
+        <v>3304904</v>
       </c>
       <c r="N309" s="7">
         <v>1</v>
@@ -18313,13 +18345,13 @@
     </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A310" s="4">
-        <v>3304904</v>
+        <v>3305406</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>252</v>
@@ -18349,7 +18381,7 @@
         <v>0</v>
       </c>
       <c r="M310" s="5">
-        <v>3304904</v>
+        <v>3305406</v>
       </c>
       <c r="N310" s="7">
         <v>1</v>
@@ -18360,13 +18392,13 @@
     </row>
     <row r="311" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
-        <v>3305406</v>
+        <v>3305505</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>252</v>
@@ -18396,7 +18428,7 @@
         <v>0</v>
       </c>
       <c r="M311" s="5">
-        <v>3305406</v>
+        <v>3305505</v>
       </c>
       <c r="N311" s="7">
         <v>1</v>
@@ -18407,13 +18439,13 @@
     </row>
     <row r="312" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
-        <v>3305505</v>
+        <v>3305604</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>252</v>
@@ -18443,7 +18475,7 @@
         <v>0</v>
       </c>
       <c r="M312" s="5">
-        <v>3305505</v>
+        <v>3305604</v>
       </c>
       <c r="N312" s="7">
         <v>1</v>
@@ -18454,13 +18486,13 @@
     </row>
     <row r="313" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
-        <v>3305604</v>
+        <v>3305703</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>252</v>
@@ -18490,7 +18522,7 @@
         <v>0</v>
       </c>
       <c r="M313" s="5">
-        <v>3305604</v>
+        <v>3305703</v>
       </c>
       <c r="N313" s="7">
         <v>1</v>
@@ -18501,13 +18533,13 @@
     </row>
     <row r="314" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
-        <v>3305703</v>
+        <v>3305752</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>526</v>
+        <v>253</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>252</v>
@@ -18537,7 +18569,7 @@
         <v>0</v>
       </c>
       <c r="M314" s="5">
-        <v>3305703</v>
+        <v>3305752</v>
       </c>
       <c r="N314" s="7">
         <v>1</v>
@@ -18548,13 +18580,13 @@
     </row>
     <row r="315" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
-        <v>3305752</v>
+        <v>3305802</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>253</v>
+        <v>528</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>252</v>
@@ -18584,7 +18616,7 @@
         <v>0</v>
       </c>
       <c r="M315" s="5">
-        <v>3305752</v>
+        <v>3305802</v>
       </c>
       <c r="N315" s="7">
         <v>1</v>
@@ -18595,19 +18627,19 @@
     </row>
     <row r="316" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A316" s="4">
-        <v>3305802</v>
+        <v>3101508</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>252</v>
+        <v>16</v>
       </c>
       <c r="E316" s="5" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="F316" s="6" t="s">
         <v>18</v>
@@ -18616,13 +18648,13 @@
         <v>19</v>
       </c>
       <c r="H316" s="5" t="s">
-        <v>503</v>
+        <v>532</v>
       </c>
       <c r="I316" s="8" t="s">
-        <v>504</v>
+        <v>533</v>
       </c>
       <c r="J316" s="5" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="K316" s="5" t="s">
         <v>21</v>
@@ -18631,24 +18663,24 @@
         <v>0</v>
       </c>
       <c r="M316" s="5">
-        <v>3305802</v>
+        <v>3101508</v>
       </c>
       <c r="N316" s="7">
         <v>1</v>
       </c>
       <c r="O316" s="6" t="s">
-        <v>505</v>
+        <v>534</v>
       </c>
     </row>
     <row r="317" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A317" s="4">
-        <v>3101508</v>
+        <v>3105509</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>16</v>
@@ -18678,7 +18710,7 @@
         <v>0</v>
       </c>
       <c r="M317" s="5">
-        <v>3101508</v>
+        <v>3105509</v>
       </c>
       <c r="N317" s="7">
         <v>1</v>
@@ -18689,13 +18721,13 @@
     </row>
     <row r="318" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A318" s="4">
-        <v>3103603</v>
+        <v>3115300</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>16</v>
@@ -18725,7 +18757,7 @@
         <v>0</v>
       </c>
       <c r="M318" s="5">
-        <v>3103603</v>
+        <v>3115300</v>
       </c>
       <c r="N318" s="7">
         <v>1</v>
@@ -18736,13 +18768,13 @@
     </row>
     <row r="319" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
-        <v>3104403</v>
+        <v>3124005</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>16</v>
@@ -18772,7 +18804,7 @@
         <v>0</v>
       </c>
       <c r="M319" s="5">
-        <v>3104403</v>
+        <v>3124005</v>
       </c>
       <c r="N319" s="7">
         <v>1</v>
@@ -18783,13 +18815,13 @@
     </row>
     <row r="320" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A320" s="4">
-        <v>3104601</v>
+        <v>3124609</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>16</v>
@@ -18819,7 +18851,7 @@
         <v>0</v>
       </c>
       <c r="M320" s="5">
-        <v>3104601</v>
+        <v>3124609</v>
       </c>
       <c r="N320" s="7">
         <v>1</v>
@@ -18830,13 +18862,13 @@
     </row>
     <row r="321" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
-        <v>3105509</v>
+        <v>3128808</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>539</v>
+        <v>562</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>16</v>
@@ -18866,7 +18898,7 @@
         <v>0</v>
       </c>
       <c r="M321" s="5">
-        <v>3105509</v>
+        <v>3128808</v>
       </c>
       <c r="N321" s="7">
         <v>1</v>
@@ -18877,13 +18909,13 @@
     </row>
     <row r="322" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A322" s="4">
-        <v>3106101</v>
+        <v>3129004</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>16</v>
@@ -18913,7 +18945,7 @@
         <v>0</v>
       </c>
       <c r="M322" s="5">
-        <v>3106101</v>
+        <v>3129004</v>
       </c>
       <c r="N322" s="7">
         <v>1</v>
@@ -18924,13 +18956,13 @@
     </row>
     <row r="323" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
-        <v>3106903</v>
+        <v>3138005</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>16</v>
@@ -18960,7 +18992,7 @@
         <v>0</v>
       </c>
       <c r="M323" s="5">
-        <v>3106903</v>
+        <v>3138005</v>
       </c>
       <c r="N323" s="7">
         <v>1</v>
@@ -18971,13 +19003,13 @@
     </row>
     <row r="324" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A324" s="4">
-        <v>3107208</v>
+        <v>3138401</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>16</v>
@@ -19007,7 +19039,7 @@
         <v>0</v>
       </c>
       <c r="M324" s="5">
-        <v>3107208</v>
+        <v>3138401</v>
       </c>
       <c r="N324" s="7">
         <v>1</v>
@@ -19018,13 +19050,13 @@
     </row>
     <row r="325" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A325" s="4">
-        <v>3107505</v>
+        <v>3142205</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>16</v>
@@ -19054,7 +19086,7 @@
         <v>0</v>
       </c>
       <c r="M325" s="5">
-        <v>3107505</v>
+        <v>3142205</v>
       </c>
       <c r="N325" s="7">
         <v>1</v>
@@ -19065,13 +19097,13 @@
     </row>
     <row r="326" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A326" s="4">
-        <v>3115300</v>
+        <v>3143906</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>544</v>
+        <v>577</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>544</v>
+        <v>578</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>16</v>
@@ -19101,7 +19133,7 @@
         <v>0</v>
       </c>
       <c r="M326" s="5">
-        <v>3115300</v>
+        <v>3143906</v>
       </c>
       <c r="N326" s="7">
         <v>1</v>
@@ -19112,13 +19144,13 @@
     </row>
     <row r="327" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A327" s="4">
-        <v>3115904</v>
+        <v>3146701</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>545</v>
+        <v>580</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>546</v>
+        <v>580</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>16</v>
@@ -19148,7 +19180,7 @@
         <v>0</v>
       </c>
       <c r="M327" s="5">
-        <v>3115904</v>
+        <v>3146701</v>
       </c>
       <c r="N327" s="7">
         <v>1</v>
@@ -19159,13 +19191,13 @@
     </row>
     <row r="328" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A328" s="4">
-        <v>3116209</v>
+        <v>3151107</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>547</v>
+        <v>585</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>547</v>
+        <v>585</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>16</v>
@@ -19195,7 +19227,7 @@
         <v>0</v>
       </c>
       <c r="M328" s="5">
-        <v>3116209</v>
+        <v>3151107</v>
       </c>
       <c r="N328" s="7">
         <v>1</v>
@@ -19206,13 +19238,13 @@
     </row>
     <row r="329" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
-        <v>3119609</v>
+        <v>3154101</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>548</v>
+        <v>586</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>548</v>
+        <v>586</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>16</v>
@@ -19242,7 +19274,7 @@
         <v>0</v>
       </c>
       <c r="M329" s="5">
-        <v>3119609</v>
+        <v>3154101</v>
       </c>
       <c r="N329" s="7">
         <v>1</v>
@@ -19253,13 +19285,13 @@
     </row>
     <row r="330" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A330" s="4">
-        <v>3121308</v>
+        <v>3156304</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>549</v>
+        <v>590</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>549</v>
+        <v>590</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>16</v>
@@ -19289,7 +19321,7 @@
         <v>0</v>
       </c>
       <c r="M330" s="5">
-        <v>3121308</v>
+        <v>3156304</v>
       </c>
       <c r="N330" s="7">
         <v>1</v>
@@ -19300,13 +19332,13 @@
     </row>
     <row r="331" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A331" s="4">
-        <v>3122900</v>
+        <v>3156452</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>550</v>
+        <v>591</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>551</v>
+        <v>592</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>16</v>
@@ -19336,7 +19368,7 @@
         <v>0</v>
       </c>
       <c r="M331" s="5">
-        <v>3122900</v>
+        <v>3156452</v>
       </c>
       <c r="N331" s="7">
         <v>1</v>
@@ -19347,13 +19379,13 @@
     </row>
     <row r="332" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A332" s="4">
-        <v>3124005</v>
+        <v>3158409</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>552</v>
+        <v>596</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>553</v>
+        <v>596</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>16</v>
@@ -19383,7 +19415,7 @@
         <v>0</v>
       </c>
       <c r="M332" s="5">
-        <v>3124005</v>
+        <v>3158409</v>
       </c>
       <c r="N332" s="7">
         <v>1</v>
@@ -19394,13 +19426,13 @@
     </row>
     <row r="333" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A333" s="4">
-        <v>3124609</v>
+        <v>3164431</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>554</v>
+        <v>602</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>554</v>
+        <v>603</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>16</v>
@@ -19430,7 +19462,7 @@
         <v>0</v>
       </c>
       <c r="M333" s="5">
-        <v>3124609</v>
+        <v>3164431</v>
       </c>
       <c r="N333" s="7">
         <v>1</v>
@@ -19441,13 +19473,13 @@
     </row>
     <row r="334" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A334" s="4">
-        <v>3125002</v>
+        <v>3172103</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>555</v>
+        <v>608</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>556</v>
+        <v>608</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>16</v>
@@ -19477,7 +19509,7 @@
         <v>0</v>
       </c>
       <c r="M334" s="5">
-        <v>3125002</v>
+        <v>3172103</v>
       </c>
       <c r="N334" s="7">
         <v>1</v>
@@ -19488,13 +19520,13 @@
     </row>
     <row r="335" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A335" s="4">
-        <v>3127388</v>
+        <v>3103603</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>16</v>
@@ -19509,13 +19541,13 @@
         <v>19</v>
       </c>
       <c r="H335" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I335" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J335" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K335" s="5" t="s">
         <v>21</v>
@@ -19524,7 +19556,7 @@
         <v>0</v>
       </c>
       <c r="M335" s="5">
-        <v>3127388</v>
+        <v>3103603</v>
       </c>
       <c r="N335" s="7">
         <v>1</v>
@@ -19535,13 +19567,13 @@
     </row>
     <row r="336" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A336" s="4">
-        <v>3128402</v>
+        <v>3104403</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>559</v>
+        <v>536</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>559</v>
+        <v>536</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>16</v>
@@ -19556,13 +19588,13 @@
         <v>19</v>
       </c>
       <c r="H336" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I336" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J336" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K336" s="5" t="s">
         <v>21</v>
@@ -19571,7 +19603,7 @@
         <v>0</v>
       </c>
       <c r="M336" s="5">
-        <v>3128402</v>
+        <v>3104403</v>
       </c>
       <c r="N336" s="7">
         <v>1</v>
@@ -19582,13 +19614,13 @@
     </row>
     <row r="337" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
-        <v>3128501</v>
+        <v>3104601</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>560</v>
+        <v>537</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>561</v>
+        <v>537</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>16</v>
@@ -19603,13 +19635,13 @@
         <v>19</v>
       </c>
       <c r="H337" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I337" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J337" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K337" s="5" t="s">
         <v>21</v>
@@ -19618,7 +19650,7 @@
         <v>0</v>
       </c>
       <c r="M337" s="5">
-        <v>3128501</v>
+        <v>3104601</v>
       </c>
       <c r="N337" s="7">
         <v>1</v>
@@ -19629,13 +19661,13 @@
     </row>
     <row r="338" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A338" s="4">
-        <v>3128808</v>
+        <v>3106101</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>16</v>
@@ -19650,13 +19682,13 @@
         <v>19</v>
       </c>
       <c r="H338" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I338" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J338" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K338" s="5" t="s">
         <v>21</v>
@@ -19665,7 +19697,7 @@
         <v>0</v>
       </c>
       <c r="M338" s="5">
-        <v>3128808</v>
+        <v>3106101</v>
       </c>
       <c r="N338" s="7">
         <v>1</v>
@@ -19676,13 +19708,13 @@
     </row>
     <row r="339" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
-        <v>3129004</v>
+        <v>3106903</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>16</v>
@@ -19697,13 +19729,13 @@
         <v>19</v>
       </c>
       <c r="H339" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I339" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J339" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K339" s="5" t="s">
         <v>21</v>
@@ -19712,7 +19744,7 @@
         <v>0</v>
       </c>
       <c r="M339" s="5">
-        <v>3129004</v>
+        <v>3106903</v>
       </c>
       <c r="N339" s="7">
         <v>1</v>
@@ -19723,13 +19755,13 @@
     </row>
     <row r="340" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A340" s="4">
-        <v>3132602</v>
+        <v>3107208</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>16</v>
@@ -19744,13 +19776,13 @@
         <v>19</v>
       </c>
       <c r="H340" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I340" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J340" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K340" s="5" t="s">
         <v>21</v>
@@ -19759,7 +19791,7 @@
         <v>0</v>
       </c>
       <c r="M340" s="5">
-        <v>3132602</v>
+        <v>3107208</v>
       </c>
       <c r="N340" s="7">
         <v>1</v>
@@ -19770,13 +19802,13 @@
     </row>
     <row r="341" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
-        <v>3133006</v>
+        <v>3107505</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>16</v>
@@ -19791,13 +19823,13 @@
         <v>19</v>
       </c>
       <c r="H341" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I341" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J341" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K341" s="5" t="s">
         <v>21</v>
@@ -19806,7 +19838,7 @@
         <v>0</v>
       </c>
       <c r="M341" s="5">
-        <v>3133006</v>
+        <v>3107505</v>
       </c>
       <c r="N341" s="7">
         <v>1</v>
@@ -19817,13 +19849,13 @@
     </row>
     <row r="342" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A342" s="4">
-        <v>3136702</v>
+        <v>3115904</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>566</v>
+        <v>546</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>16</v>
@@ -19838,13 +19870,13 @@
         <v>19</v>
       </c>
       <c r="H342" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I342" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J342" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K342" s="5" t="s">
         <v>21</v>
@@ -19853,7 +19885,7 @@
         <v>0</v>
       </c>
       <c r="M342" s="5">
-        <v>3136702</v>
+        <v>3115904</v>
       </c>
       <c r="N342" s="7">
         <v>1</v>
@@ -19864,13 +19896,13 @@
     </row>
     <row r="343" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
-        <v>3138005</v>
+        <v>3116209</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>16</v>
@@ -19885,13 +19917,13 @@
         <v>19</v>
       </c>
       <c r="H343" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I343" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J343" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K343" s="5" t="s">
         <v>21</v>
@@ -19900,7 +19932,7 @@
         <v>0</v>
       </c>
       <c r="M343" s="5">
-        <v>3138005</v>
+        <v>3116209</v>
       </c>
       <c r="N343" s="7">
         <v>1</v>
@@ -19911,13 +19943,13 @@
     </row>
     <row r="344" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A344" s="4">
-        <v>3138401</v>
+        <v>3119609</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>16</v>
@@ -19932,13 +19964,13 @@
         <v>19</v>
       </c>
       <c r="H344" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I344" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J344" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K344" s="5" t="s">
         <v>21</v>
@@ -19947,7 +19979,7 @@
         <v>0</v>
       </c>
       <c r="M344" s="5">
-        <v>3138401</v>
+        <v>3119609</v>
       </c>
       <c r="N344" s="7">
         <v>1</v>
@@ -19958,13 +19990,13 @@
     </row>
     <row r="345" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
-        <v>3138500</v>
+        <v>3121308</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>569</v>
+        <v>549</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>569</v>
+        <v>549</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>16</v>
@@ -19979,13 +20011,13 @@
         <v>19</v>
       </c>
       <c r="H345" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I345" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J345" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K345" s="5" t="s">
         <v>21</v>
@@ -19994,7 +20026,7 @@
         <v>0</v>
       </c>
       <c r="M345" s="5">
-        <v>3138500</v>
+        <v>3121308</v>
       </c>
       <c r="N345" s="7">
         <v>1</v>
@@ -20005,13 +20037,13 @@
     </row>
     <row r="346" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A346" s="4">
-        <v>3138609</v>
+        <v>3122900</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>16</v>
@@ -20026,13 +20058,13 @@
         <v>19</v>
       </c>
       <c r="H346" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I346" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J346" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K346" s="5" t="s">
         <v>21</v>
@@ -20041,7 +20073,7 @@
         <v>0</v>
       </c>
       <c r="M346" s="5">
-        <v>3138609</v>
+        <v>3122900</v>
       </c>
       <c r="N346" s="7">
         <v>1</v>
@@ -20052,13 +20084,13 @@
     </row>
     <row r="347" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
-        <v>3139805</v>
+        <v>3125002</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>16</v>
@@ -20073,13 +20105,13 @@
         <v>19</v>
       </c>
       <c r="H347" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I347" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J347" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K347" s="5" t="s">
         <v>21</v>
@@ -20088,7 +20120,7 @@
         <v>0</v>
       </c>
       <c r="M347" s="5">
-        <v>3139805</v>
+        <v>3125002</v>
       </c>
       <c r="N347" s="7">
         <v>1</v>
@@ -20099,13 +20131,13 @@
     </row>
     <row r="348" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A348" s="4">
-        <v>3140209</v>
+        <v>3127388</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>16</v>
@@ -20120,13 +20152,13 @@
         <v>19</v>
       </c>
       <c r="H348" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I348" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J348" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K348" s="5" t="s">
         <v>21</v>
@@ -20135,7 +20167,7 @@
         <v>0</v>
       </c>
       <c r="M348" s="5">
-        <v>3140209</v>
+        <v>3127388</v>
       </c>
       <c r="N348" s="7">
         <v>1</v>
@@ -20146,13 +20178,13 @@
     </row>
     <row r="349" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
-        <v>3140803</v>
+        <v>3128402</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>16</v>
@@ -20167,13 +20199,13 @@
         <v>19</v>
       </c>
       <c r="H349" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I349" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J349" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K349" s="5" t="s">
         <v>21</v>
@@ -20182,7 +20214,7 @@
         <v>0</v>
       </c>
       <c r="M349" s="5">
-        <v>3140803</v>
+        <v>3128402</v>
       </c>
       <c r="N349" s="7">
         <v>1</v>
@@ -20193,13 +20225,13 @@
     </row>
     <row r="350" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A350" s="4">
-        <v>3142205</v>
+        <v>3128501</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>575</v>
+        <v>560</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>16</v>
@@ -20214,13 +20246,13 @@
         <v>19</v>
       </c>
       <c r="H350" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I350" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J350" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K350" s="5" t="s">
         <v>21</v>
@@ -20229,7 +20261,7 @@
         <v>0</v>
       </c>
       <c r="M350" s="5">
-        <v>3142205</v>
+        <v>3128501</v>
       </c>
       <c r="N350" s="7">
         <v>1</v>
@@ -20240,13 +20272,13 @@
     </row>
     <row r="351" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
-        <v>3143906</v>
+        <v>3132602</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>16</v>
@@ -20261,13 +20293,13 @@
         <v>19</v>
       </c>
       <c r="H351" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I351" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J351" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K351" s="5" t="s">
         <v>21</v>
@@ -20276,7 +20308,7 @@
         <v>0</v>
       </c>
       <c r="M351" s="5">
-        <v>3143906</v>
+        <v>3132602</v>
       </c>
       <c r="N351" s="7">
         <v>1</v>
@@ -20287,13 +20319,13 @@
     </row>
     <row r="352" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A352" s="4">
-        <v>3145406</v>
+        <v>3133006</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>16</v>
@@ -20308,13 +20340,13 @@
         <v>19</v>
       </c>
       <c r="H352" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I352" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J352" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K352" s="5" t="s">
         <v>21</v>
@@ -20323,7 +20355,7 @@
         <v>0</v>
       </c>
       <c r="M352" s="5">
-        <v>3145406</v>
+        <v>3133006</v>
       </c>
       <c r="N352" s="7">
         <v>1</v>
@@ -20334,13 +20366,13 @@
     </row>
     <row r="353" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
-        <v>3146701</v>
+        <v>3136702</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>16</v>
@@ -20355,13 +20387,13 @@
         <v>19</v>
       </c>
       <c r="H353" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I353" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J353" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K353" s="5" t="s">
         <v>21</v>
@@ -20370,7 +20402,7 @@
         <v>0</v>
       </c>
       <c r="M353" s="5">
-        <v>3146701</v>
+        <v>3136702</v>
       </c>
       <c r="N353" s="7">
         <v>1</v>
@@ -20381,13 +20413,13 @@
     </row>
     <row r="354" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A354" s="4">
-        <v>3147808</v>
+        <v>3138500</v>
       </c>
       <c r="B354" s="5" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>16</v>
@@ -20402,13 +20434,13 @@
         <v>19</v>
       </c>
       <c r="H354" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I354" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J354" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K354" s="5" t="s">
         <v>21</v>
@@ -20417,7 +20449,7 @@
         <v>0</v>
       </c>
       <c r="M354" s="5">
-        <v>3147808</v>
+        <v>3138500</v>
       </c>
       <c r="N354" s="7">
         <v>1</v>
@@ -20428,13 +20460,13 @@
     </row>
     <row r="355" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
-        <v>3149408</v>
+        <v>3138609</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>16</v>
@@ -20449,13 +20481,13 @@
         <v>19</v>
       </c>
       <c r="H355" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I355" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J355" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K355" s="5" t="s">
         <v>21</v>
@@ -20464,7 +20496,7 @@
         <v>0</v>
       </c>
       <c r="M355" s="5">
-        <v>3149408</v>
+        <v>3138609</v>
       </c>
       <c r="N355" s="7">
         <v>1</v>
@@ -20475,13 +20507,13 @@
     </row>
     <row r="356" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A356" s="4">
-        <v>3149507</v>
+        <v>3139805</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>16</v>
@@ -20496,13 +20528,13 @@
         <v>19</v>
       </c>
       <c r="H356" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I356" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J356" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K356" s="5" t="s">
         <v>21</v>
@@ -20511,7 +20543,7 @@
         <v>0</v>
       </c>
       <c r="M356" s="5">
-        <v>3149507</v>
+        <v>3139805</v>
       </c>
       <c r="N356" s="7">
         <v>1</v>
@@ -20522,13 +20554,13 @@
     </row>
     <row r="357" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
-        <v>3150109</v>
+        <v>3140209</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>16</v>
@@ -20543,13 +20575,13 @@
         <v>19</v>
       </c>
       <c r="H357" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I357" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J357" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K357" s="5" t="s">
         <v>21</v>
@@ -20558,7 +20590,7 @@
         <v>0</v>
       </c>
       <c r="M357" s="5">
-        <v>3150109</v>
+        <v>3140209</v>
       </c>
       <c r="N357" s="7">
         <v>1</v>
@@ -20569,13 +20601,13 @@
     </row>
     <row r="358" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
-        <v>3151107</v>
+        <v>3140803</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>16</v>
@@ -20590,13 +20622,13 @@
         <v>19</v>
       </c>
       <c r="H358" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I358" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J358" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K358" s="5" t="s">
         <v>21</v>
@@ -20605,7 +20637,7 @@
         <v>0</v>
       </c>
       <c r="M358" s="5">
-        <v>3151107</v>
+        <v>3140803</v>
       </c>
       <c r="N358" s="7">
         <v>1</v>
@@ -20616,13 +20648,13 @@
     </row>
     <row r="359" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
-        <v>3154101</v>
+        <v>3145406</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>16</v>
@@ -20637,13 +20669,13 @@
         <v>19</v>
       </c>
       <c r="H359" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I359" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J359" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K359" s="5" t="s">
         <v>21</v>
@@ -20652,7 +20684,7 @@
         <v>0</v>
       </c>
       <c r="M359" s="5">
-        <v>3154101</v>
+        <v>3145406</v>
       </c>
       <c r="N359" s="7">
         <v>1</v>
@@ -20663,13 +20695,13 @@
     </row>
     <row r="360" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
-        <v>3155405</v>
+        <v>3147808</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>16</v>
@@ -20684,13 +20716,13 @@
         <v>19</v>
       </c>
       <c r="H360" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I360" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J360" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K360" s="5" t="s">
         <v>21</v>
@@ -20699,7 +20731,7 @@
         <v>0</v>
       </c>
       <c r="M360" s="5">
-        <v>3155405</v>
+        <v>3147808</v>
       </c>
       <c r="N360" s="7">
         <v>1</v>
@@ -20710,13 +20742,13 @@
     </row>
     <row r="361" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
-        <v>3155900</v>
+        <v>3149408</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>16</v>
@@ -20731,13 +20763,13 @@
         <v>19</v>
       </c>
       <c r="H361" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I361" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J361" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K361" s="5" t="s">
         <v>21</v>
@@ -20746,7 +20778,7 @@
         <v>0</v>
       </c>
       <c r="M361" s="5">
-        <v>3155900</v>
+        <v>3149408</v>
       </c>
       <c r="N361" s="7">
         <v>1</v>
@@ -20757,13 +20789,13 @@
     </row>
     <row r="362" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A362" s="4">
-        <v>3156205</v>
+        <v>3149507</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>16</v>
@@ -20778,13 +20810,13 @@
         <v>19</v>
       </c>
       <c r="H362" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I362" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J362" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K362" s="5" t="s">
         <v>21</v>
@@ -20793,7 +20825,7 @@
         <v>0</v>
       </c>
       <c r="M362" s="5">
-        <v>3156205</v>
+        <v>3149507</v>
       </c>
       <c r="N362" s="7">
         <v>1</v>
@@ -20804,13 +20836,13 @@
     </row>
     <row r="363" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
-        <v>3156304</v>
+        <v>3150109</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>16</v>
@@ -20825,13 +20857,13 @@
         <v>19</v>
       </c>
       <c r="H363" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I363" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J363" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K363" s="5" t="s">
         <v>21</v>
@@ -20840,7 +20872,7 @@
         <v>0</v>
       </c>
       <c r="M363" s="5">
-        <v>3156304</v>
+        <v>3150109</v>
       </c>
       <c r="N363" s="7">
         <v>1</v>
@@ -20851,13 +20883,13 @@
     </row>
     <row r="364" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A364" s="4">
-        <v>3156452</v>
+        <v>3155405</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>16</v>
@@ -20872,13 +20904,13 @@
         <v>19</v>
       </c>
       <c r="H364" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I364" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J364" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K364" s="5" t="s">
         <v>21</v>
@@ -20887,7 +20919,7 @@
         <v>0</v>
       </c>
       <c r="M364" s="5">
-        <v>3156452</v>
+        <v>3155405</v>
       </c>
       <c r="N364" s="7">
         <v>1</v>
@@ -20898,13 +20930,13 @@
     </row>
     <row r="365" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
-        <v>3157278</v>
+        <v>3155900</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>16</v>
@@ -20919,13 +20951,13 @@
         <v>19</v>
       </c>
       <c r="H365" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I365" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J365" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K365" s="5" t="s">
         <v>21</v>
@@ -20934,7 +20966,7 @@
         <v>0</v>
       </c>
       <c r="M365" s="5">
-        <v>3157278</v>
+        <v>3155900</v>
       </c>
       <c r="N365" s="7">
         <v>1</v>
@@ -20945,13 +20977,13 @@
     </row>
     <row r="366" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A366" s="4">
-        <v>3159308</v>
+        <v>3156205</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>16</v>
@@ -20966,13 +20998,13 @@
         <v>19</v>
       </c>
       <c r="H366" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I366" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J366" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K366" s="5" t="s">
         <v>21</v>
@@ -20981,7 +21013,7 @@
         <v>0</v>
       </c>
       <c r="M366" s="5">
-        <v>3159308</v>
+        <v>3156205</v>
       </c>
       <c r="N366" s="7">
         <v>1</v>
@@ -20992,13 +21024,13 @@
     </row>
     <row r="367" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A367" s="4">
-        <v>3158409</v>
+        <v>3157278</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>16</v>
@@ -21013,13 +21045,13 @@
         <v>19</v>
       </c>
       <c r="H367" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I367" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J367" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K367" s="5" t="s">
         <v>21</v>
@@ -21028,7 +21060,7 @@
         <v>0</v>
       </c>
       <c r="M367" s="5">
-        <v>3158409</v>
+        <v>3157278</v>
       </c>
       <c r="N367" s="7">
         <v>1</v>
@@ -21039,13 +21071,13 @@
     </row>
     <row r="368" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A368" s="4">
-        <v>3158607</v>
+        <v>3159308</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>16</v>
@@ -21060,13 +21092,13 @@
         <v>19</v>
       </c>
       <c r="H368" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I368" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J368" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K368" s="5" t="s">
         <v>21</v>
@@ -21075,7 +21107,7 @@
         <v>0</v>
       </c>
       <c r="M368" s="5">
-        <v>3158607</v>
+        <v>3159308</v>
       </c>
       <c r="N368" s="7">
         <v>1</v>
@@ -21086,13 +21118,13 @@
     </row>
     <row r="369" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A369" s="4">
-        <v>3160009</v>
+        <v>3158607</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>16</v>
@@ -21107,13 +21139,13 @@
         <v>19</v>
       </c>
       <c r="H369" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I369" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J369" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K369" s="5" t="s">
         <v>21</v>
@@ -21122,7 +21154,7 @@
         <v>0</v>
       </c>
       <c r="M369" s="5">
-        <v>3160009</v>
+        <v>3158607</v>
       </c>
       <c r="N369" s="7">
         <v>1</v>
@@ -21133,13 +21165,13 @@
     </row>
     <row r="370" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A370" s="4">
-        <v>3162906</v>
+        <v>3160009</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>16</v>
@@ -21154,13 +21186,13 @@
         <v>19</v>
       </c>
       <c r="H370" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I370" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J370" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K370" s="5" t="s">
         <v>21</v>
@@ -21169,7 +21201,7 @@
         <v>0</v>
       </c>
       <c r="M370" s="5">
-        <v>3162906</v>
+        <v>3160009</v>
       </c>
       <c r="N370" s="7">
         <v>1</v>
@@ -21180,13 +21212,13 @@
     </row>
     <row r="371" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A371" s="4">
-        <v>3164431</v>
+        <v>3162906</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>16</v>
@@ -21201,13 +21233,13 @@
         <v>19</v>
       </c>
       <c r="H371" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I371" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J371" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K371" s="5" t="s">
         <v>21</v>
@@ -21216,7 +21248,7 @@
         <v>0</v>
       </c>
       <c r="M371" s="5">
-        <v>3164431</v>
+        <v>3162906</v>
       </c>
       <c r="N371" s="7">
         <v>1</v>
@@ -21248,13 +21280,13 @@
         <v>19</v>
       </c>
       <c r="H372" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I372" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J372" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K372" s="5" t="s">
         <v>21</v>
@@ -21295,13 +21327,13 @@
         <v>19</v>
       </c>
       <c r="H373" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I373" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J373" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K373" s="5" t="s">
         <v>21</v>
@@ -21342,13 +21374,13 @@
         <v>19</v>
       </c>
       <c r="H374" s="5" t="s">
-        <v>532</v>
+        <v>983</v>
       </c>
       <c r="I374" s="8" t="s">
-        <v>533</v>
+        <v>983</v>
       </c>
       <c r="J374" s="5" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="K374" s="5" t="s">
         <v>21</v>
@@ -21368,19 +21400,19 @@
     </row>
     <row r="375" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A375" s="4">
-        <v>3172103</v>
+        <v>2927705</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="E375" s="5" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F375" s="6" t="s">
         <v>18</v>
@@ -21389,13 +21421,13 @@
         <v>19</v>
       </c>
       <c r="H375" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="I375" s="8" t="s">
-        <v>533</v>
+        <v>611</v>
+      </c>
+      <c r="I375" s="5" t="s">
+        <v>611</v>
       </c>
       <c r="J375" s="5" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="K375" s="5" t="s">
         <v>21</v>
@@ -21404,30 +21436,30 @@
         <v>0</v>
       </c>
       <c r="M375" s="5">
-        <v>3172103</v>
+        <v>2927705</v>
       </c>
       <c r="N375" s="7">
         <v>1</v>
       </c>
       <c r="O375" s="6" t="s">
-        <v>534</v>
+        <v>612</v>
       </c>
     </row>
     <row r="376" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A376" s="4">
-        <v>2927705</v>
+        <v>3203056</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E376" s="5" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="F376" s="6" t="s">
         <v>18</v>
@@ -21436,13 +21468,13 @@
         <v>19</v>
       </c>
       <c r="H376" s="5" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="I376" s="5" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="J376" s="5" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="K376" s="5" t="s">
         <v>21</v>
@@ -21451,24 +21483,24 @@
         <v>0</v>
       </c>
       <c r="M376" s="5">
-        <v>2927705</v>
+        <v>3203056</v>
       </c>
       <c r="N376" s="7">
         <v>1</v>
       </c>
       <c r="O376" s="6" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="377" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A377" s="4">
-        <v>3203056</v>
+        <v>3204906</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>78</v>
@@ -21498,7 +21530,7 @@
         <v>0</v>
       </c>
       <c r="M377" s="5">
-        <v>3203056</v>
+        <v>3204906</v>
       </c>
       <c r="N377" s="7">
         <v>1</v>
@@ -21509,13 +21541,13 @@
     </row>
     <row r="378" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A378" s="4">
-        <v>3204906</v>
+        <v>3205176</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>78</v>
@@ -21539,16 +21571,16 @@
         <v>972</v>
       </c>
       <c r="K378" s="5" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L378" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M378" s="5">
-        <v>3204906</v>
+        <v>32051762</v>
       </c>
       <c r="N378" s="7">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="O378" s="6" t="s">
         <v>616</v>
@@ -21556,19 +21588,19 @@
     </row>
     <row r="379" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A379" s="4">
-        <v>3205176</v>
+        <v>3200300</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>78</v>
       </c>
       <c r="E379" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="F379" s="6" t="s">
         <v>18</v>
@@ -21577,39 +21609,39 @@
         <v>19</v>
       </c>
       <c r="H379" s="5" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="I379" s="5" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="J379" s="5" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K379" s="5" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L379" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M379" s="5">
-        <v>32051762</v>
+        <v>3200300</v>
       </c>
       <c r="N379" s="7">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="O379" s="6" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="380" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A380" s="4">
-        <v>3200300</v>
+        <v>3200409</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>78</v>
@@ -21639,7 +21671,7 @@
         <v>0</v>
       </c>
       <c r="M380" s="5">
-        <v>3200300</v>
+        <v>3200409</v>
       </c>
       <c r="N380" s="7">
         <v>1</v>
@@ -21650,13 +21682,13 @@
     </row>
     <row r="381" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A381" s="4">
-        <v>3200409</v>
+        <v>3200706</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>78</v>
@@ -21686,7 +21718,7 @@
         <v>0</v>
       </c>
       <c r="M381" s="5">
-        <v>3200409</v>
+        <v>3200706</v>
       </c>
       <c r="N381" s="7">
         <v>1</v>
@@ -21697,13 +21729,13 @@
     </row>
     <row r="382" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A382" s="4">
-        <v>3200706</v>
+        <v>3201209</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>78</v>
@@ -21733,7 +21765,7 @@
         <v>0</v>
       </c>
       <c r="M382" s="5">
-        <v>3200706</v>
+        <v>3201209</v>
       </c>
       <c r="N382" s="7">
         <v>1</v>
@@ -21744,13 +21776,13 @@
     </row>
     <row r="383" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A383" s="4">
-        <v>3201209</v>
+        <v>3201407</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>78</v>
@@ -21780,7 +21812,7 @@
         <v>0</v>
       </c>
       <c r="M383" s="5">
-        <v>3201209</v>
+        <v>3201407</v>
       </c>
       <c r="N383" s="7">
         <v>1</v>
@@ -21791,13 +21823,13 @@
     </row>
     <row r="384" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A384" s="4">
-        <v>3201407</v>
+        <v>3202603</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>78</v>
@@ -21827,7 +21859,7 @@
         <v>0</v>
       </c>
       <c r="M384" s="5">
-        <v>3201407</v>
+        <v>3202603</v>
       </c>
       <c r="N384" s="7">
         <v>1</v>
@@ -21838,13 +21870,13 @@
     </row>
     <row r="385" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A385" s="4">
-        <v>3202603</v>
+        <v>3202801</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>78</v>
@@ -21874,7 +21906,7 @@
         <v>0</v>
       </c>
       <c r="M385" s="5">
-        <v>3202603</v>
+        <v>3202801</v>
       </c>
       <c r="N385" s="7">
         <v>1</v>
@@ -21885,13 +21917,13 @@
     </row>
     <row r="386" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A386" s="4">
-        <v>3202801</v>
+        <v>3203320</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>78</v>
@@ -21921,7 +21953,7 @@
         <v>0</v>
       </c>
       <c r="M386" s="5">
-        <v>3202801</v>
+        <v>3203320</v>
       </c>
       <c r="N386" s="7">
         <v>1</v>
@@ -21932,13 +21964,13 @@
     </row>
     <row r="387" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A387" s="4">
-        <v>3203320</v>
+        <v>3203346</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>78</v>
@@ -21968,7 +22000,7 @@
         <v>0</v>
       </c>
       <c r="M387" s="5">
-        <v>3203320</v>
+        <v>3203346</v>
       </c>
       <c r="N387" s="7">
         <v>1</v>
@@ -21979,13 +22011,13 @@
     </row>
     <row r="388" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A388" s="4">
-        <v>3203346</v>
+        <v>3204203</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>78</v>
@@ -22015,7 +22047,7 @@
         <v>0</v>
       </c>
       <c r="M388" s="5">
-        <v>3203346</v>
+        <v>3204203</v>
       </c>
       <c r="N388" s="7">
         <v>1</v>
@@ -22026,13 +22058,13 @@
     </row>
     <row r="389" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A389" s="4">
-        <v>3204203</v>
+        <v>3204302</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>78</v>
@@ -22062,7 +22094,7 @@
         <v>0</v>
       </c>
       <c r="M389" s="5">
-        <v>3204203</v>
+        <v>3204302</v>
       </c>
       <c r="N389" s="7">
         <v>1</v>
@@ -22073,13 +22105,13 @@
     </row>
     <row r="390" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A390" s="4">
-        <v>3204302</v>
+        <v>3204401</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>78</v>
@@ -22109,7 +22141,7 @@
         <v>0</v>
       </c>
       <c r="M390" s="5">
-        <v>3204302</v>
+        <v>3204401</v>
       </c>
       <c r="N390" s="7">
         <v>1</v>
@@ -22120,13 +22152,13 @@
     </row>
     <row r="391" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A391" s="4">
-        <v>3204401</v>
+        <v>3205036</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>78</v>
@@ -22156,7 +22188,7 @@
         <v>0</v>
       </c>
       <c r="M391" s="5">
-        <v>3204401</v>
+        <v>3205036</v>
       </c>
       <c r="N391" s="7">
         <v>1</v>
@@ -22167,19 +22199,19 @@
     </row>
     <row r="392" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A392" s="4">
-        <v>3205036</v>
+        <v>3119203</v>
       </c>
       <c r="B392" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="E392" s="5" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="F392" s="6" t="s">
         <v>18</v>
@@ -22188,13 +22220,13 @@
         <v>19</v>
       </c>
       <c r="H392" s="5" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="I392" s="5" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="J392" s="5" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="K392" s="5" t="s">
         <v>21</v>
@@ -22203,24 +22235,24 @@
         <v>0</v>
       </c>
       <c r="M392" s="5">
-        <v>3205036</v>
+        <v>3119203</v>
       </c>
       <c r="N392" s="7">
         <v>1</v>
       </c>
       <c r="O392" s="6" t="s">
-        <v>623</v>
+        <v>22</v>
       </c>
     </row>
     <row r="393" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A393" s="4">
-        <v>3119203</v>
+        <v>3100609</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>16</v>
@@ -22250,24 +22282,24 @@
         <v>0</v>
       </c>
       <c r="M393" s="5">
-        <v>3119203</v>
+        <v>3100609</v>
       </c>
       <c r="N393" s="7">
         <v>1</v>
       </c>
       <c r="O393" s="6" t="s">
-        <v>22</v>
+        <v>643</v>
       </c>
     </row>
     <row r="394" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A394" s="4">
-        <v>3100609</v>
+        <v>3102407</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>16</v>
@@ -22297,7 +22329,7 @@
         <v>0</v>
       </c>
       <c r="M394" s="5">
-        <v>3100609</v>
+        <v>3102407</v>
       </c>
       <c r="N394" s="7">
         <v>1</v>
@@ -22308,13 +22340,13 @@
     </row>
     <row r="395" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A395" s="4">
-        <v>3102407</v>
+        <v>3102852</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>16</v>
@@ -22344,7 +22376,7 @@
         <v>0</v>
       </c>
       <c r="M395" s="5">
-        <v>3102407</v>
+        <v>3102852</v>
       </c>
       <c r="N395" s="7">
         <v>1</v>
@@ -22355,13 +22387,13 @@
     </row>
     <row r="396" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A396" s="4">
-        <v>3102852</v>
+        <v>3104452</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>16</v>
@@ -22391,7 +22423,7 @@
         <v>0</v>
       </c>
       <c r="M396" s="5">
-        <v>3102852</v>
+        <v>3104452</v>
       </c>
       <c r="N396" s="7">
         <v>1</v>
@@ -22402,13 +22434,13 @@
     </row>
     <row r="397" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A397" s="4">
-        <v>3104452</v>
+        <v>3112059</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>647</v>
+        <v>264</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>647</v>
+        <v>264</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>16</v>
@@ -22438,7 +22470,7 @@
         <v>0</v>
       </c>
       <c r="M397" s="5">
-        <v>3104452</v>
+        <v>3112059</v>
       </c>
       <c r="N397" s="7">
         <v>1</v>
@@ -22449,13 +22481,13 @@
     </row>
     <row r="398" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A398" s="4">
-        <v>3112059</v>
+        <v>3112307</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>264</v>
+        <v>648</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>264</v>
+        <v>648</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>16</v>
@@ -22485,7 +22517,7 @@
         <v>0</v>
       </c>
       <c r="M398" s="5">
-        <v>3112059</v>
+        <v>3112307</v>
       </c>
       <c r="N398" s="7">
         <v>1</v>
@@ -22496,13 +22528,13 @@
     </row>
     <row r="399" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A399" s="4">
-        <v>3112307</v>
+        <v>3116803</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>16</v>
@@ -22532,7 +22564,7 @@
         <v>0</v>
       </c>
       <c r="M399" s="5">
-        <v>3112307</v>
+        <v>3116803</v>
       </c>
       <c r="N399" s="7">
         <v>1</v>
@@ -22543,13 +22575,13 @@
     </row>
     <row r="400" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A400" s="4">
-        <v>3116803</v>
+        <v>3122603</v>
       </c>
       <c r="B400" s="5" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>16</v>
@@ -22579,7 +22611,7 @@
         <v>0</v>
       </c>
       <c r="M400" s="5">
-        <v>3116803</v>
+        <v>3122603</v>
       </c>
       <c r="N400" s="7">
         <v>1</v>
@@ -22590,13 +22622,13 @@
     </row>
     <row r="401" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A401" s="4">
-        <v>3122603</v>
+        <v>3126950</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>16</v>
@@ -22626,7 +22658,7 @@
         <v>0</v>
       </c>
       <c r="M401" s="5">
-        <v>3122603</v>
+        <v>3126950</v>
       </c>
       <c r="N401" s="7">
         <v>1</v>
@@ -22637,13 +22669,13 @@
     </row>
     <row r="402" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A402" s="4">
-        <v>3126950</v>
+        <v>3132503</v>
       </c>
       <c r="B402" s="5" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>16</v>
@@ -22673,7 +22705,7 @@
         <v>0</v>
       </c>
       <c r="M402" s="5">
-        <v>3126950</v>
+        <v>3132503</v>
       </c>
       <c r="N402" s="7">
         <v>1</v>
@@ -22684,13 +22716,13 @@
     </row>
     <row r="403" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A403" s="4">
-        <v>3132503</v>
+        <v>3136553</v>
       </c>
       <c r="B403" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>16</v>
@@ -22720,7 +22752,7 @@
         <v>0</v>
       </c>
       <c r="M403" s="5">
-        <v>3132503</v>
+        <v>3136553</v>
       </c>
       <c r="N403" s="7">
         <v>1</v>
@@ -22731,13 +22763,13 @@
     </row>
     <row r="404" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A404" s="4">
-        <v>3136553</v>
+        <v>3140605</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>16</v>
@@ -22767,7 +22799,7 @@
         <v>0</v>
       </c>
       <c r="M404" s="5">
-        <v>3136553</v>
+        <v>3140605</v>
       </c>
       <c r="N404" s="7">
         <v>1</v>
@@ -22778,13 +22810,13 @@
     </row>
     <row r="405" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A405" s="4">
-        <v>3140605</v>
+        <v>3141801</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>16</v>
@@ -22814,7 +22846,7 @@
         <v>0</v>
       </c>
       <c r="M405" s="5">
-        <v>3140605</v>
+        <v>3141801</v>
       </c>
       <c r="N405" s="7">
         <v>1</v>
@@ -22825,13 +22857,13 @@
     </row>
     <row r="406" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A406" s="4">
-        <v>3141801</v>
+        <v>3148400</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>16</v>
@@ -22861,7 +22893,7 @@
         <v>0</v>
       </c>
       <c r="M406" s="5">
-        <v>3141801</v>
+        <v>3148400</v>
       </c>
       <c r="N406" s="7">
         <v>1</v>
@@ -22872,13 +22904,13 @@
     </row>
     <row r="407" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A407" s="4">
-        <v>3148400</v>
+        <v>3148608</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>16</v>
@@ -22908,7 +22940,7 @@
         <v>0</v>
       </c>
       <c r="M407" s="5">
-        <v>3148400</v>
+        <v>3148608</v>
       </c>
       <c r="N407" s="7">
         <v>1</v>
@@ -22919,13 +22951,13 @@
     </row>
     <row r="408" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A408" s="4">
-        <v>3148608</v>
+        <v>3156007</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>16</v>
@@ -22955,7 +22987,7 @@
         <v>0</v>
       </c>
       <c r="M408" s="5">
-        <v>3148608</v>
+        <v>3156007</v>
       </c>
       <c r="N408" s="7">
         <v>1</v>
@@ -22966,13 +22998,13 @@
     </row>
     <row r="409" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A409" s="4">
-        <v>3156007</v>
+        <v>3156809</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>16</v>
@@ -23002,7 +23034,7 @@
         <v>0</v>
       </c>
       <c r="M409" s="5">
-        <v>3156007</v>
+        <v>3156809</v>
       </c>
       <c r="N409" s="7">
         <v>1</v>
@@ -23013,13 +23045,13 @@
     </row>
     <row r="410" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A410" s="4">
-        <v>3156809</v>
+        <v>3158201</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>16</v>
@@ -23049,7 +23081,7 @@
         <v>0</v>
       </c>
       <c r="M410" s="5">
-        <v>3156809</v>
+        <v>3158201</v>
       </c>
       <c r="N410" s="7">
         <v>1</v>
@@ -23060,13 +23092,13 @@
     </row>
     <row r="411" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A411" s="4">
-        <v>3158201</v>
+        <v>3160207</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>16</v>
@@ -23096,7 +23128,7 @@
         <v>0</v>
       </c>
       <c r="M411" s="5">
-        <v>3158201</v>
+        <v>3160207</v>
       </c>
       <c r="N411" s="7">
         <v>1</v>
@@ -23107,13 +23139,13 @@
     </row>
     <row r="412" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A412" s="4">
-        <v>3160207</v>
+        <v>3162807</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>16</v>
@@ -23143,7 +23175,7 @@
         <v>0</v>
       </c>
       <c r="M412" s="5">
-        <v>3160207</v>
+        <v>3162807</v>
       </c>
       <c r="N412" s="7">
         <v>1</v>
@@ -23154,13 +23186,13 @@
     </row>
     <row r="413" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A413" s="4">
-        <v>3162807</v>
+        <v>3163508</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>16</v>
@@ -23190,7 +23222,7 @@
         <v>0</v>
       </c>
       <c r="M413" s="5">
-        <v>3162807</v>
+        <v>3163508</v>
       </c>
       <c r="N413" s="7">
         <v>1</v>
@@ -23201,13 +23233,13 @@
     </row>
     <row r="414" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A414" s="4">
-        <v>3163508</v>
+        <v>3164100</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>16</v>
@@ -23237,7 +23269,7 @@
         <v>0</v>
       </c>
       <c r="M414" s="5">
-        <v>3163508</v>
+        <v>3164100</v>
       </c>
       <c r="N414" s="7">
         <v>1</v>
@@ -23248,13 +23280,13 @@
     </row>
     <row r="415" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A415" s="4">
-        <v>3164100</v>
+        <v>3164506</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>16</v>
@@ -23284,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="M415" s="5">
-        <v>3164100</v>
+        <v>3164506</v>
       </c>
       <c r="N415" s="7">
         <v>1</v>
@@ -23295,13 +23327,13 @@
     </row>
     <row r="416" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A416" s="4">
-        <v>3164506</v>
+        <v>3166501</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>16</v>
@@ -23331,7 +23363,7 @@
         <v>0</v>
       </c>
       <c r="M416" s="5">
-        <v>3164506</v>
+        <v>3166501</v>
       </c>
       <c r="N416" s="7">
         <v>1</v>
@@ -23342,13 +23374,13 @@
     </row>
     <row r="417" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A417" s="4">
-        <v>3166501</v>
+        <v>3167103</v>
       </c>
       <c r="B417" s="5" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>16</v>
@@ -23378,7 +23410,7 @@
         <v>0</v>
       </c>
       <c r="M417" s="5">
-        <v>3166501</v>
+        <v>3167103</v>
       </c>
       <c r="N417" s="7">
         <v>1</v>
@@ -23389,13 +23421,13 @@
     </row>
     <row r="418" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A418" s="4">
-        <v>3167103</v>
+        <v>3169703</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>16</v>
@@ -23425,7 +23457,7 @@
         <v>0</v>
       </c>
       <c r="M418" s="5">
-        <v>3167103</v>
+        <v>3169703</v>
       </c>
       <c r="N418" s="7">
         <v>1</v>
@@ -23436,13 +23468,13 @@
     </row>
     <row r="419" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A419" s="4">
-        <v>3169703</v>
+        <v>3171071</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>16</v>
@@ -23472,7 +23504,7 @@
         <v>0</v>
       </c>
       <c r="M419" s="5">
-        <v>3169703</v>
+        <v>3171071</v>
       </c>
       <c r="N419" s="7">
         <v>1</v>
@@ -23483,13 +23515,13 @@
     </row>
     <row r="420" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A420" s="4">
-        <v>3171071</v>
+        <v>3135456</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>16</v>
@@ -23519,30 +23551,30 @@
         <v>0</v>
       </c>
       <c r="M420" s="5">
-        <v>3171071</v>
+        <v>3135456</v>
       </c>
       <c r="N420" s="7">
         <v>1</v>
       </c>
       <c r="O420" s="6" t="s">
-        <v>643</v>
+        <v>349</v>
       </c>
     </row>
     <row r="421" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A421" s="4">
-        <v>3135456</v>
+        <v>3200169</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E421" s="5" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="F421" s="6" t="s">
         <v>18</v>
@@ -23551,13 +23583,13 @@
         <v>19</v>
       </c>
       <c r="H421" s="5" t="s">
-        <v>640</v>
+        <v>683</v>
       </c>
       <c r="I421" s="5" t="s">
-        <v>640</v>
+        <v>683</v>
       </c>
       <c r="J421" s="5" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="K421" s="5" t="s">
         <v>21</v>
@@ -23566,24 +23598,24 @@
         <v>0</v>
       </c>
       <c r="M421" s="5">
-        <v>3135456</v>
+        <v>3200169</v>
       </c>
       <c r="N421" s="7">
         <v>1</v>
       </c>
       <c r="O421" s="6" t="s">
-        <v>349</v>
+        <v>684</v>
       </c>
     </row>
     <row r="422" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A422" s="4">
-        <v>3200169</v>
+        <v>3200136</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>78</v>
@@ -23613,7 +23645,7 @@
         <v>0</v>
       </c>
       <c r="M422" s="5">
-        <v>3200169</v>
+        <v>3200136</v>
       </c>
       <c r="N422" s="7">
         <v>1</v>
@@ -23624,13 +23656,13 @@
     </row>
     <row r="423" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A423" s="4">
-        <v>3200136</v>
+        <v>3200904</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>78</v>
@@ -23660,7 +23692,7 @@
         <v>0</v>
       </c>
       <c r="M423" s="5">
-        <v>3200136</v>
+        <v>3200904</v>
       </c>
       <c r="N423" s="7">
         <v>1</v>
@@ -23671,13 +23703,13 @@
     </row>
     <row r="424" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A424" s="4">
-        <v>3200904</v>
+        <v>3201001</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>78</v>
@@ -23707,7 +23739,7 @@
         <v>0</v>
       </c>
       <c r="M424" s="5">
-        <v>3200904</v>
+        <v>3201001</v>
       </c>
       <c r="N424" s="7">
         <v>1</v>
@@ -23718,13 +23750,13 @@
     </row>
     <row r="425" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A425" s="4">
-        <v>3201001</v>
+        <v>3203908</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>78</v>
@@ -23754,7 +23786,7 @@
         <v>0</v>
       </c>
       <c r="M425" s="5">
-        <v>3201001</v>
+        <v>3203908</v>
       </c>
       <c r="N425" s="7">
         <v>1</v>
@@ -23765,13 +23797,13 @@
     </row>
     <row r="426" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A426" s="4">
-        <v>3203908</v>
+        <v>3204104</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>78</v>
@@ -23801,7 +23833,7 @@
         <v>0</v>
       </c>
       <c r="M426" s="5">
-        <v>3203908</v>
+        <v>3204104</v>
       </c>
       <c r="N426" s="7">
         <v>1</v>
@@ -23812,13 +23844,13 @@
     </row>
     <row r="427" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A427" s="4">
-        <v>3204104</v>
+        <v>3205150</v>
       </c>
       <c r="B427" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>78</v>
@@ -23848,7 +23880,7 @@
         <v>0</v>
       </c>
       <c r="M427" s="5">
-        <v>3204104</v>
+        <v>3205150</v>
       </c>
       <c r="N427" s="7">
         <v>1</v>
@@ -23859,13 +23891,13 @@
     </row>
     <row r="428" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A428" s="4">
-        <v>3205150</v>
+        <v>3200607</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>78</v>
@@ -23880,13 +23912,13 @@
         <v>19</v>
       </c>
       <c r="H428" s="5" t="s">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="I428" s="5" t="s">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="J428" s="5" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="K428" s="5" t="s">
         <v>21</v>
@@ -23895,24 +23927,24 @@
         <v>0</v>
       </c>
       <c r="M428" s="5">
-        <v>3205150</v>
+        <v>3200607</v>
       </c>
       <c r="N428" s="7">
         <v>1</v>
       </c>
       <c r="O428" s="6" t="s">
-        <v>684</v>
+        <v>84</v>
       </c>
     </row>
     <row r="429" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A429" s="4">
-        <v>3200607</v>
+        <v>3202207</v>
       </c>
       <c r="B429" s="5" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>78</v>
@@ -23942,7 +23974,7 @@
         <v>0</v>
       </c>
       <c r="M429" s="5">
-        <v>3200607</v>
+        <v>3202207</v>
       </c>
       <c r="N429" s="7">
         <v>1</v>
@@ -23953,13 +23985,13 @@
     </row>
     <row r="430" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A430" s="4">
-        <v>3202207</v>
+        <v>3202504</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C430" s="5" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>78</v>
@@ -23989,7 +24021,7 @@
         <v>0</v>
       </c>
       <c r="M430" s="5">
-        <v>3202207</v>
+        <v>3202504</v>
       </c>
       <c r="N430" s="7">
         <v>1</v>
@@ -24000,13 +24032,13 @@
     </row>
     <row r="431" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A431" s="4">
-        <v>3202504</v>
+        <v>3203130</v>
       </c>
       <c r="B431" s="5" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>78</v>
@@ -24036,7 +24068,7 @@
         <v>0</v>
       </c>
       <c r="M431" s="5">
-        <v>3202504</v>
+        <v>3203130</v>
       </c>
       <c r="N431" s="7">
         <v>1</v>
@@ -24047,13 +24079,13 @@
     </row>
     <row r="432" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A432" s="4">
-        <v>3203130</v>
+        <v>3205002</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>78</v>
@@ -24083,7 +24115,7 @@
         <v>0</v>
       </c>
       <c r="M432" s="5">
-        <v>3203130</v>
+        <v>3205002</v>
       </c>
       <c r="N432" s="7">
         <v>1</v>
@@ -24094,13 +24126,13 @@
     </row>
     <row r="433" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A433" s="4">
-        <v>3205002</v>
+        <v>3203205</v>
       </c>
       <c r="B433" s="5" t="s">
-        <v>704</v>
+        <v>79</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>704</v>
+        <v>79</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>78</v>
@@ -24124,66 +24156,66 @@
         <v>976</v>
       </c>
       <c r="K433" s="5" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L433" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M433" s="5">
-        <v>3205002</v>
+        <v>32032053</v>
       </c>
       <c r="N433" s="7">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O433" s="6" t="s">
-        <v>84</v>
+        <v>705</v>
       </c>
     </row>
     <row r="434" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A434" s="4">
-        <v>3203205</v>
+        <v>2200806</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>79</v>
+        <v>440</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>79</v>
+        <v>441</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="E434" s="5" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="F434" s="6" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="G434" s="6" t="s">
         <v>19</v>
       </c>
       <c r="H434" s="5" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="I434" s="5" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="J434" s="5" t="s">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="K434" s="5" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L434" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M434" s="5">
-        <v>32032053</v>
+        <v>2200806</v>
       </c>
       <c r="N434" s="7">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O434" s="6" t="s">
-        <v>705</v>
+        <v>437</v>
       </c>
     </row>
     <row r="435" spans="1:15" x14ac:dyDescent="0.25">
@@ -31621,26 +31653,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B96036E30F13644F923D207E371C305D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d197ceb99055fd1a93a3a14aec1bdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f76aa77c-8923-4724-9a6d-d588cc513697" xmlns:ns3="89c54d5b-05ac-45d5-9242-aabb385cc5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b86266bfd619f312673123d0bd20d23" ns2:_="" ns3:_="">
     <xsd:import namespace="f76aa77c-8923-4724-9a6d-d588cc513697"/>
@@ -31835,10 +31847,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2885D72-BA50-450C-BD4C-761032353625}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DD8DB1C-B818-4A72-BFFB-70B7361B4E7B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31855,5 +31898,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DD8DB1C-B818-4A72-BFFB-70B7361B4E7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2885D72-BA50-450C-BD4C-761032353625}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/dados/territorio.xlsx
+++ b/dados/territorio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929296D5-E8A8-41D3-B22C-0862CB7EBC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63C39F7-5F40-4DB6-9092-7F60DF7DB1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31647,6 +31647,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B96036E30F13644F923D207E371C305D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d197ceb99055fd1a93a3a14aec1bdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f76aa77c-8923-4724-9a6d-d588cc513697" xmlns:ns3="89c54d5b-05ac-45d5-9242-aabb385cc5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b86266bfd619f312673123d0bd20d23" ns2:_="" ns3:_="">
     <xsd:import namespace="f76aa77c-8923-4724-9a6d-d588cc513697"/>
@@ -31841,27 +31861,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2885D72-BA50-450C-BD4C-761032353625}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{936B77CC-5081-4CE5-BAAC-5F890F495FBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DD8DB1C-B818-4A72-BFFB-70B7361B4E7B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31878,23 +31897,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{936B77CC-5081-4CE5-BAAC-5F890F495FBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
-    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2885D72-BA50-450C-BD4C-761032353625}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>